--- a/data/ALAI UP Client-level Reporting Tool Template.xlsx
+++ b/data/ALAI UP Client-level Reporting Tool Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kmlab\Desktop\Dashboard\alai_up_local_dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F6E627-5740-4D2A-A650-31299FD0C002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB06F967-7753-4E37-BF6E-3E329C943F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-9840" windowWidth="29040" windowHeight="15720" xr2:uid="{500E2EE0-B1C5-4ACF-BC67-EDC8BDABD2D7}"/>
   </bookViews>
@@ -909,9 +909,6 @@
     <t>1=Satisfaction with current regimen; 2=Fear/dislike of needles; 3=Frequency of clinic visits; 4=Concerns about cost; 5=Concerns about side effects; 6=Concerns about newness of modality; 20=Other; UNK=Unknown</t>
   </si>
   <si>
-    <t>1=Satisfaction with previous regimen; 2=Fear/dislike of needles; 3=Frequency of visit schedule; 4=Concerns about cost; 5=Concerns about newness of modality; 6=Failing treatment; 7=Lost to follow up; 8=Concerns about side effects; 9=Switched out of clinic; 10=Change/loss of insurance/payor; 20=Other</t>
-  </si>
-  <si>
     <t>0=Sustained; 1=Discontinued; UNK=Unknown</t>
   </si>
   <si>
@@ -1268,6 +1265,9 @@
   </si>
   <si>
     <t>Report payor of HIV medications if different or supplemental from health care coverage. If there is no secondary payor, this field may be left blank</t>
+  </si>
+  <si>
+    <t>1=Satisfaction with previous regimen; 2=Fear/dislike of needles; 3=Frequency of visit schedule; 4=Concerns about cost; 5=Concerns about newness of modality; 6=Failing treatment; 7=Lost to follow up; 8=Concerns about side effects; 9=Switched out of clinic; 10=Change/loss of insurance/payor; 11=emergent resistance; 20=Other</t>
   </si>
 </sst>
 </file>
@@ -1887,24 +1887,6 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1914,13 +1896,13 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1930,6 +1912,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1950,7 +1941,16 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2365,7 +2365,7 @@
       <c r="K2" s="4"/>
     </row>
     <row r="3" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="122" t="s">
+      <c r="B3" s="116" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="98" t="s">
@@ -2387,7 +2387,7 @@
       <c r="I3" s="8"/>
     </row>
     <row r="4" spans="1:11" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="123"/>
+      <c r="B4" s="117"/>
       <c r="C4" s="15" t="s">
         <v>11</v>
       </c>
@@ -2407,7 +2407,7 @@
       <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:11" ht="44.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="123"/>
+      <c r="B5" s="117"/>
       <c r="C5" s="15" t="s">
         <v>15</v>
       </c>
@@ -2427,18 +2427,18 @@
       <c r="I5" s="17"/>
     </row>
     <row r="6" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B6" s="123"/>
+      <c r="B6" s="117"/>
       <c r="C6" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="D6" s="16" t="s">
         <v>323</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="E6" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="F6" s="16" t="s">
         <v>325</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>326</v>
       </c>
       <c r="G6" s="16" t="s">
         <v>270</v>
@@ -2447,7 +2447,7 @@
     </row>
     <row r="7" spans="1:11" s="19" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7"/>
-      <c r="B7" s="123"/>
+      <c r="B7" s="117"/>
       <c r="C7" s="15" t="s">
         <v>20</v>
       </c>
@@ -2469,7 +2469,7 @@
       <c r="K7" s="18"/>
     </row>
     <row r="8" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="123"/>
+      <c r="B8" s="117"/>
       <c r="C8" s="15" t="s">
         <v>24</v>
       </c>
@@ -2488,7 +2488,7 @@
       <c r="H8" s="12"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="123"/>
+      <c r="B9" s="117"/>
       <c r="C9" s="15" t="s">
         <v>28</v>
       </c>
@@ -2507,7 +2507,7 @@
       <c r="H9" s="12"/>
     </row>
     <row r="10" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B10" s="123"/>
+      <c r="B10" s="117"/>
       <c r="C10" s="15" t="s">
         <v>32</v>
       </c>
@@ -2526,7 +2526,7 @@
       <c r="H10" s="12"/>
     </row>
     <row r="11" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="123"/>
+      <c r="B11" s="117"/>
       <c r="C11" s="15" t="s">
         <v>36</v>
       </c>
@@ -2545,7 +2545,7 @@
       <c r="H11" s="12"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B12" s="123"/>
+      <c r="B12" s="117"/>
       <c r="C12" s="15" t="s">
         <v>40</v>
       </c>
@@ -2564,7 +2564,7 @@
       <c r="H12" s="12"/>
     </row>
     <row r="13" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B13" s="123"/>
+      <c r="B13" s="117"/>
       <c r="C13" s="15" t="s">
         <v>44</v>
       </c>
@@ -2583,7 +2583,7 @@
       <c r="H13" s="12"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="123"/>
+      <c r="B14" s="117"/>
       <c r="C14" s="15" t="s">
         <v>48</v>
       </c>
@@ -2602,7 +2602,7 @@
       <c r="H14" s="12"/>
     </row>
     <row r="15" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B15" s="123"/>
+      <c r="B15" s="117"/>
       <c r="C15" s="15" t="s">
         <v>51</v>
       </c>
@@ -2621,7 +2621,7 @@
       <c r="H15" s="20"/>
     </row>
     <row r="16" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B16" s="124"/>
+      <c r="B16" s="118"/>
       <c r="C16" s="15" t="s">
         <v>55</v>
       </c>
@@ -2640,10 +2640,10 @@
       <c r="H16" s="12"/>
     </row>
     <row r="17" spans="1:8" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="131" t="s">
-        <v>283</v>
-      </c>
-      <c r="B17" s="110" t="s">
+      <c r="A17" s="113" t="s">
+        <v>282</v>
+      </c>
+      <c r="B17" s="119" t="s">
         <v>59</v>
       </c>
       <c r="C17" s="100" t="s">
@@ -2652,8 +2652,8 @@
       <c r="D17" s="101" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="110" t="s">
-        <v>331</v>
+      <c r="E17" s="119" t="s">
+        <v>330</v>
       </c>
       <c r="F17" s="101" t="s">
         <v>62</v>
@@ -2664,15 +2664,15 @@
       <c r="H17" s="12"/>
     </row>
     <row r="18" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="131"/>
-      <c r="B18" s="111"/>
+      <c r="A18" s="113"/>
+      <c r="B18" s="120"/>
       <c r="C18" s="100" t="s">
         <v>63</v>
       </c>
       <c r="D18" s="101" t="s">
         <v>64</v>
       </c>
-      <c r="E18" s="111"/>
+      <c r="E18" s="120"/>
       <c r="F18" s="101" t="s">
         <v>62</v>
       </c>
@@ -2682,15 +2682,15 @@
       <c r="H18" s="12"/>
     </row>
     <row r="19" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="131"/>
-      <c r="B19" s="111"/>
+      <c r="A19" s="113"/>
+      <c r="B19" s="120"/>
       <c r="C19" s="100" t="s">
         <v>65</v>
       </c>
       <c r="D19" s="101" t="s">
         <v>66</v>
       </c>
-      <c r="E19" s="111"/>
+      <c r="E19" s="120"/>
       <c r="F19" s="101" t="s">
         <v>62</v>
       </c>
@@ -2700,15 +2700,15 @@
       <c r="H19" s="12"/>
     </row>
     <row r="20" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="131"/>
-      <c r="B20" s="111"/>
+      <c r="A20" s="113"/>
+      <c r="B20" s="120"/>
       <c r="C20" s="100" t="s">
         <v>67</v>
       </c>
       <c r="D20" s="101" t="s">
         <v>68</v>
       </c>
-      <c r="E20" s="111"/>
+      <c r="E20" s="120"/>
       <c r="F20" s="101" t="s">
         <v>62</v>
       </c>
@@ -2718,15 +2718,15 @@
       <c r="H20" s="12"/>
     </row>
     <row r="21" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="131"/>
-      <c r="B21" s="111"/>
+      <c r="A21" s="113"/>
+      <c r="B21" s="120"/>
       <c r="C21" s="100" t="s">
         <v>69</v>
       </c>
       <c r="D21" s="101" t="s">
         <v>70</v>
       </c>
-      <c r="E21" s="111"/>
+      <c r="E21" s="120"/>
       <c r="F21" s="101" t="s">
         <v>62</v>
       </c>
@@ -2736,15 +2736,15 @@
       <c r="H21" s="12"/>
     </row>
     <row r="22" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="131"/>
-      <c r="B22" s="111"/>
+      <c r="A22" s="113"/>
+      <c r="B22" s="120"/>
       <c r="C22" s="100" t="s">
         <v>252</v>
       </c>
       <c r="D22" s="101" t="s">
         <v>257</v>
       </c>
-      <c r="E22" s="111"/>
+      <c r="E22" s="120"/>
       <c r="F22" s="101" t="s">
         <v>62</v>
       </c>
@@ -2754,15 +2754,15 @@
       <c r="H22" s="12"/>
     </row>
     <row r="23" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="131"/>
-      <c r="B23" s="111"/>
+      <c r="A23" s="113"/>
+      <c r="B23" s="120"/>
       <c r="C23" s="100" t="s">
         <v>253</v>
       </c>
       <c r="D23" s="101" t="s">
         <v>258</v>
       </c>
-      <c r="E23" s="111"/>
+      <c r="E23" s="120"/>
       <c r="F23" s="101" t="s">
         <v>62</v>
       </c>
@@ -2772,15 +2772,15 @@
       <c r="H23" s="12"/>
     </row>
     <row r="24" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="131"/>
-      <c r="B24" s="111"/>
+      <c r="A24" s="113"/>
+      <c r="B24" s="120"/>
       <c r="C24" s="100" t="s">
         <v>254</v>
       </c>
       <c r="D24" s="101" t="s">
         <v>259</v>
       </c>
-      <c r="E24" s="111"/>
+      <c r="E24" s="120"/>
       <c r="F24" s="101" t="s">
         <v>62</v>
       </c>
@@ -2790,15 +2790,15 @@
       <c r="H24" s="12"/>
     </row>
     <row r="25" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="131"/>
-      <c r="B25" s="111"/>
+      <c r="A25" s="113"/>
+      <c r="B25" s="120"/>
       <c r="C25" s="100" t="s">
         <v>255</v>
       </c>
       <c r="D25" s="101" t="s">
         <v>260</v>
       </c>
-      <c r="E25" s="111"/>
+      <c r="E25" s="120"/>
       <c r="F25" s="101" t="s">
         <v>62</v>
       </c>
@@ -2808,15 +2808,15 @@
       <c r="H25" s="12"/>
     </row>
     <row r="26" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A26" s="131"/>
-      <c r="B26" s="112"/>
+      <c r="A26" s="113"/>
+      <c r="B26" s="121"/>
       <c r="C26" s="100" t="s">
         <v>256</v>
       </c>
       <c r="D26" s="101" t="s">
         <v>261</v>
       </c>
-      <c r="E26" s="112"/>
+      <c r="E26" s="121"/>
       <c r="F26" s="101" t="s">
         <v>62</v>
       </c>
@@ -2826,7 +2826,7 @@
       <c r="H26" s="12"/>
     </row>
     <row r="27" spans="1:8" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="125" t="s">
+      <c r="B27" s="122" t="s">
         <v>71</v>
       </c>
       <c r="C27" s="102" t="s">
@@ -2847,7 +2847,7 @@
       <c r="H27" s="12"/>
     </row>
     <row r="28" spans="1:8" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="126"/>
+      <c r="B28" s="123"/>
       <c r="C28" s="102" t="s">
         <v>76</v>
       </c>
@@ -2866,7 +2866,7 @@
       <c r="H28" s="12"/>
     </row>
     <row r="29" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B29" s="127"/>
+      <c r="B29" s="124"/>
       <c r="C29" s="102" t="s">
         <v>80</v>
       </c>
@@ -2885,20 +2885,20 @@
       <c r="H29" s="12"/>
     </row>
     <row r="30" spans="1:8" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="B30" s="128" t="s">
+      <c r="B30" s="125" t="s">
         <v>84</v>
       </c>
       <c r="C30" s="103" t="s">
+        <v>361</v>
+      </c>
+      <c r="D30" s="23" t="s">
         <v>362</v>
-      </c>
-      <c r="D30" s="23" t="s">
-        <v>363</v>
       </c>
       <c r="E30" s="23" t="s">
         <v>85</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G30" s="23" t="s">
         <v>270</v>
@@ -2906,18 +2906,18 @@
       <c r="H30" s="24"/>
     </row>
     <row r="31" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B31" s="129"/>
+      <c r="B31" s="126"/>
       <c r="C31" s="103" t="s">
+        <v>363</v>
+      </c>
+      <c r="D31" s="23" t="s">
         <v>364</v>
       </c>
-      <c r="D31" s="23" t="s">
+      <c r="E31" s="23" t="s">
+        <v>366</v>
+      </c>
+      <c r="F31" s="23" t="s">
         <v>365</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>367</v>
-      </c>
-      <c r="F31" s="23" t="s">
-        <v>366</v>
       </c>
       <c r="G31" s="23" t="s">
         <v>269</v>
@@ -2925,7 +2925,7 @@
       <c r="H31" s="24"/>
     </row>
     <row r="32" spans="1:8" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="129"/>
+      <c r="B32" s="126"/>
       <c r="C32" s="103" t="s">
         <v>86</v>
       </c>
@@ -2944,7 +2944,7 @@
       <c r="H32" s="24"/>
     </row>
     <row r="33" spans="1:11" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="129"/>
+      <c r="B33" s="126"/>
       <c r="C33" s="103" t="s">
         <v>89</v>
       </c>
@@ -2963,7 +2963,7 @@
       <c r="H33" s="12"/>
     </row>
     <row r="34" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B34" s="129"/>
+      <c r="B34" s="126"/>
       <c r="C34" s="103" t="s">
         <v>93</v>
       </c>
@@ -2982,7 +2982,7 @@
       <c r="H34" s="10"/>
     </row>
     <row r="35" spans="1:11" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="129"/>
+      <c r="B35" s="126"/>
       <c r="C35" s="103" t="s">
         <v>97</v>
       </c>
@@ -3001,7 +3001,7 @@
       <c r="H35" s="12"/>
     </row>
     <row r="36" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B36" s="129"/>
+      <c r="B36" s="126"/>
       <c r="C36" s="103" t="s">
         <v>101</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>102</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F36" s="23" t="s">
         <v>103</v>
@@ -3020,7 +3020,7 @@
       <c r="H36" s="24"/>
     </row>
     <row r="37" spans="1:11" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="129"/>
+      <c r="B37" s="126"/>
       <c r="C37" s="103" t="s">
         <v>104</v>
       </c>
@@ -3039,7 +3039,7 @@
       <c r="H37" s="12"/>
     </row>
     <row r="38" spans="1:11" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="B38" s="129"/>
+      <c r="B38" s="126"/>
       <c r="C38" s="103" t="s">
         <v>107</v>
       </c>
@@ -3059,15 +3059,15 @@
     </row>
     <row r="39" spans="1:11" ht="63" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="84"/>
-      <c r="B39" s="129"/>
+      <c r="B39" s="126"/>
       <c r="C39" s="103" t="s">
         <v>248</v>
       </c>
       <c r="D39" s="104" t="s">
         <v>249</v>
       </c>
-      <c r="E39" s="113" t="s">
-        <v>332</v>
+      <c r="E39" s="128" t="s">
+        <v>331</v>
       </c>
       <c r="F39" s="104"/>
       <c r="G39" s="104" t="s">
@@ -3077,14 +3077,14 @@
     </row>
     <row r="40" spans="1:11" ht="63" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="84"/>
-      <c r="B40" s="129"/>
+      <c r="B40" s="126"/>
       <c r="C40" s="103" t="s">
         <v>250</v>
       </c>
       <c r="D40" s="104" t="s">
         <v>249</v>
       </c>
-      <c r="E40" s="114"/>
+      <c r="E40" s="129"/>
       <c r="F40" s="104"/>
       <c r="G40" s="104" t="s">
         <v>269</v>
@@ -3093,14 +3093,14 @@
     </row>
     <row r="41" spans="1:11" ht="63" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="84"/>
-      <c r="B41" s="130"/>
+      <c r="B41" s="127"/>
       <c r="C41" s="103" t="s">
         <v>251</v>
       </c>
       <c r="D41" s="104" t="s">
         <v>249</v>
       </c>
-      <c r="E41" s="115"/>
+      <c r="E41" s="130"/>
       <c r="F41" s="104"/>
       <c r="G41" s="104" t="s">
         <v>269</v>
@@ -3108,8 +3108,8 @@
       <c r="H41" s="12"/>
     </row>
     <row r="42" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B42" s="119" t="s">
-        <v>278</v>
+      <c r="B42" s="114" t="s">
+        <v>277</v>
       </c>
       <c r="C42" s="26" t="s">
         <v>240</v>
@@ -3129,7 +3129,7 @@
       <c r="H42" s="24"/>
     </row>
     <row r="43" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B43" s="120"/>
+      <c r="B43" s="115"/>
       <c r="C43" s="26" t="s">
         <v>241</v>
       </c>
@@ -3148,7 +3148,7 @@
       <c r="H43" s="24"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B44" s="121"/>
+      <c r="B44" s="131"/>
       <c r="C44" s="26" t="s">
         <v>262</v>
       </c>
@@ -3167,11 +3167,11 @@
       <c r="H44" s="24"/>
     </row>
     <row r="45" spans="1:11" s="29" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="131" t="s">
-        <v>290</v>
-      </c>
-      <c r="B45" s="119" t="s">
-        <v>284</v>
+      <c r="A45" s="113" t="s">
+        <v>289</v>
+      </c>
+      <c r="B45" s="114" t="s">
+        <v>283</v>
       </c>
       <c r="C45" s="105" t="s">
         <v>116</v>
@@ -3194,8 +3194,8 @@
       <c r="K45" s="28"/>
     </row>
     <row r="46" spans="1:11" s="29" customFormat="1" ht="224.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="131"/>
-      <c r="B46" s="120"/>
+      <c r="A46" s="113"/>
+      <c r="B46" s="115"/>
       <c r="C46" s="105" t="s">
         <v>118</v>
       </c>
@@ -3203,7 +3203,7 @@
         <v>119</v>
       </c>
       <c r="E46" s="105" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F46" s="26" t="s">
         <v>112</v>
@@ -3217,9 +3217,9 @@
       <c r="K46" s="28"/>
     </row>
     <row r="47" spans="1:11" s="29" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="131"/>
-      <c r="B47" s="119" t="s">
-        <v>285</v>
+      <c r="A47" s="113"/>
+      <c r="B47" s="114" t="s">
+        <v>284</v>
       </c>
       <c r="C47" s="105" t="s">
         <v>120</v>
@@ -3242,8 +3242,8 @@
       <c r="K47" s="28"/>
     </row>
     <row r="48" spans="1:11" s="29" customFormat="1" ht="224.4" x14ac:dyDescent="0.3">
-      <c r="A48" s="131"/>
-      <c r="B48" s="120"/>
+      <c r="A48" s="113"/>
+      <c r="B48" s="115"/>
       <c r="C48" s="105" t="s">
         <v>122</v>
       </c>
@@ -3251,7 +3251,7 @@
         <v>123</v>
       </c>
       <c r="E48" s="105" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F48" s="26" t="s">
         <v>112</v>
@@ -3266,7 +3266,7 @@
     </row>
     <row r="49" spans="1:11" s="33" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A49"/>
-      <c r="B49" s="116" t="s">
+      <c r="B49" s="110" t="s">
         <v>140</v>
       </c>
       <c r="C49" s="36" t="s">
@@ -3291,7 +3291,7 @@
     </row>
     <row r="50" spans="1:11" s="33" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A50"/>
-      <c r="B50" s="118"/>
+      <c r="B50" s="112"/>
       <c r="C50" s="36" t="s">
         <v>144</v>
       </c>
@@ -3313,11 +3313,11 @@
       <c r="K50" s="32"/>
     </row>
     <row r="51" spans="1:11" s="33" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="131" t="s">
-        <v>291</v>
-      </c>
-      <c r="B51" s="116" t="s">
-        <v>286</v>
+      <c r="A51" s="113" t="s">
+        <v>290</v>
+      </c>
+      <c r="B51" s="110" t="s">
+        <v>285</v>
       </c>
       <c r="C51" s="36" t="s">
         <v>148</v>
@@ -3340,8 +3340,8 @@
       <c r="K51" s="32"/>
     </row>
     <row r="52" spans="1:11" s="33" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="131"/>
-      <c r="B52" s="117"/>
+      <c r="A52" s="113"/>
+      <c r="B52" s="111"/>
       <c r="C52" s="36" t="s">
         <v>151</v>
       </c>
@@ -3363,8 +3363,8 @@
       <c r="K52" s="32"/>
     </row>
     <row r="53" spans="1:11" s="33" customFormat="1" ht="290.39999999999998" x14ac:dyDescent="0.3">
-      <c r="A53" s="131"/>
-      <c r="B53" s="117"/>
+      <c r="A53" s="113"/>
+      <c r="B53" s="111"/>
       <c r="C53" s="36" t="s">
         <v>155</v>
       </c>
@@ -3372,7 +3372,7 @@
         <v>156</v>
       </c>
       <c r="E53" s="37" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F53" s="36" t="s">
         <v>275</v>
@@ -3386,8 +3386,8 @@
       <c r="K53" s="32"/>
     </row>
     <row r="54" spans="1:11" s="33" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="131"/>
-      <c r="B54" s="118"/>
+      <c r="A54" s="113"/>
+      <c r="B54" s="112"/>
       <c r="C54" s="36" t="s">
         <v>157</v>
       </c>
@@ -3409,11 +3409,11 @@
       <c r="K54" s="32"/>
     </row>
     <row r="55" spans="1:11" s="33" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="131" t="s">
-        <v>292</v>
-      </c>
-      <c r="B55" s="116" t="s">
-        <v>289</v>
+      <c r="A55" s="113" t="s">
+        <v>291</v>
+      </c>
+      <c r="B55" s="110" t="s">
+        <v>288</v>
       </c>
       <c r="C55" s="36" t="s">
         <v>160</v>
@@ -3436,8 +3436,8 @@
       <c r="K55" s="32"/>
     </row>
     <row r="56" spans="1:11" s="33" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="131"/>
-      <c r="B56" s="117"/>
+      <c r="A56" s="113"/>
+      <c r="B56" s="111"/>
       <c r="C56" s="36" t="s">
         <v>163</v>
       </c>
@@ -3459,8 +3459,8 @@
       <c r="K56" s="32"/>
     </row>
     <row r="57" spans="1:11" s="33" customFormat="1" ht="356.4" x14ac:dyDescent="0.3">
-      <c r="A57" s="131"/>
-      <c r="B57" s="117"/>
+      <c r="A57" s="113"/>
+      <c r="B57" s="111"/>
       <c r="C57" s="36" t="s">
         <v>167</v>
       </c>
@@ -3468,10 +3468,10 @@
         <v>168</v>
       </c>
       <c r="E57" s="37" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F57" s="37" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G57" s="36" t="s">
         <v>265</v>
@@ -3482,10 +3482,10 @@
       <c r="K57" s="32"/>
     </row>
     <row r="58" spans="1:11" s="33" customFormat="1" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A58" s="131"/>
-      <c r="B58" s="118"/>
+      <c r="A58" s="113"/>
+      <c r="B58" s="112"/>
       <c r="C58" s="36" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D58" s="37" t="s">
         <v>169</v>
@@ -3505,11 +3505,11 @@
       <c r="K58" s="32"/>
     </row>
     <row r="59" spans="1:11" s="33" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="131" t="s">
-        <v>291</v>
-      </c>
-      <c r="B59" s="116" t="s">
-        <v>288</v>
+      <c r="A59" s="113" t="s">
+        <v>290</v>
+      </c>
+      <c r="B59" s="110" t="s">
+        <v>287</v>
       </c>
       <c r="C59" s="36" t="s">
         <v>170</v>
@@ -3532,8 +3532,8 @@
       <c r="K59" s="32"/>
     </row>
     <row r="60" spans="1:11" s="33" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="131"/>
-      <c r="B60" s="117"/>
+      <c r="A60" s="113"/>
+      <c r="B60" s="111"/>
       <c r="C60" s="36" t="s">
         <v>173</v>
       </c>
@@ -3555,8 +3555,8 @@
       <c r="K60" s="32"/>
     </row>
     <row r="61" spans="1:11" s="33" customFormat="1" ht="290.39999999999998" x14ac:dyDescent="0.3">
-      <c r="A61" s="131"/>
-      <c r="B61" s="117"/>
+      <c r="A61" s="113"/>
+      <c r="B61" s="111"/>
       <c r="C61" s="36" t="s">
         <v>175</v>
       </c>
@@ -3564,7 +3564,7 @@
         <v>176</v>
       </c>
       <c r="E61" s="37" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F61" s="36" t="s">
         <v>275</v>
@@ -3578,8 +3578,8 @@
       <c r="K61" s="32"/>
     </row>
     <row r="62" spans="1:11" s="33" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="131"/>
-      <c r="B62" s="118"/>
+      <c r="A62" s="113"/>
+      <c r="B62" s="112"/>
       <c r="C62" s="36" t="s">
         <v>177</v>
       </c>
@@ -3601,11 +3601,11 @@
       <c r="K62" s="32"/>
     </row>
     <row r="63" spans="1:11" s="33" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="131" t="s">
-        <v>292</v>
-      </c>
-      <c r="B63" s="116" t="s">
-        <v>287</v>
+      <c r="A63" s="113" t="s">
+        <v>291</v>
+      </c>
+      <c r="B63" s="110" t="s">
+        <v>286</v>
       </c>
       <c r="C63" s="36" t="s">
         <v>179</v>
@@ -3628,8 +3628,8 @@
       <c r="K63" s="32"/>
     </row>
     <row r="64" spans="1:11" s="33" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="131"/>
-      <c r="B64" s="117"/>
+      <c r="A64" s="113"/>
+      <c r="B64" s="111"/>
       <c r="C64" s="36" t="s">
         <v>182</v>
       </c>
@@ -3651,8 +3651,8 @@
       <c r="K64" s="32"/>
     </row>
     <row r="65" spans="1:11" ht="356.4" x14ac:dyDescent="0.3">
-      <c r="A65" s="131"/>
-      <c r="B65" s="117"/>
+      <c r="A65" s="113"/>
+      <c r="B65" s="111"/>
       <c r="C65" s="36" t="s">
         <v>185</v>
       </c>
@@ -3660,10 +3660,10 @@
         <v>186</v>
       </c>
       <c r="E65" s="37" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F65" s="37" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G65" s="36" t="s">
         <v>265</v>
@@ -3671,10 +3671,10 @@
       <c r="H65" s="12"/>
     </row>
     <row r="66" spans="1:11" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A66" s="131"/>
-      <c r="B66" s="118"/>
+      <c r="A66" s="113"/>
+      <c r="B66" s="112"/>
       <c r="C66" s="36" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D66" s="37" t="s">
         <v>187</v>
@@ -3691,8 +3691,8 @@
       <c r="H66" s="12"/>
     </row>
     <row r="67" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B67" s="116" t="s">
-        <v>279</v>
+      <c r="B67" s="110" t="s">
+        <v>278</v>
       </c>
       <c r="C67" s="36" t="s">
         <v>188</v>
@@ -3701,7 +3701,7 @@
         <v>189</v>
       </c>
       <c r="E67" s="37" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F67" s="36" t="s">
         <v>190</v>
@@ -3712,7 +3712,7 @@
       <c r="H67" s="10"/>
     </row>
     <row r="68" spans="1:11" ht="93" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="117"/>
+      <c r="B68" s="111"/>
       <c r="C68" s="36" t="s">
         <v>191</v>
       </c>
@@ -3720,7 +3720,7 @@
         <v>192</v>
       </c>
       <c r="E68" s="37" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F68" s="36" t="s">
         <v>112</v>
@@ -3731,18 +3731,18 @@
       <c r="H68" s="12"/>
     </row>
     <row r="69" spans="1:11" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="117"/>
+      <c r="B69" s="111"/>
       <c r="C69" s="36" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D69" s="37" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E69" s="37" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F69" s="36" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G69" s="36" t="s">
         <v>270</v>
@@ -3750,18 +3750,18 @@
       <c r="H69" s="12"/>
     </row>
     <row r="70" spans="1:11" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="117"/>
+      <c r="B70" s="111"/>
       <c r="C70" s="36" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D70" s="37" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E70" s="37" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F70" s="36" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G70" s="36" t="s">
         <v>270</v>
@@ -3769,12 +3769,12 @@
       <c r="H70" s="12"/>
     </row>
     <row r="71" spans="1:11" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="118"/>
+      <c r="B71" s="112"/>
       <c r="C71" s="36" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D71" s="37" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E71" s="37" t="s">
         <v>159</v>
@@ -3788,11 +3788,11 @@
       <c r="H71" s="12"/>
     </row>
     <row r="72" spans="1:11" s="29" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A72" s="131" t="s">
-        <v>293</v>
-      </c>
-      <c r="B72" s="116" t="s">
-        <v>280</v>
+      <c r="A72" s="113" t="s">
+        <v>292</v>
+      </c>
+      <c r="B72" s="110" t="s">
+        <v>279</v>
       </c>
       <c r="C72" s="36" t="s">
         <v>193</v>
@@ -3815,8 +3815,8 @@
       <c r="K72" s="28"/>
     </row>
     <row r="73" spans="1:11" s="29" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A73" s="131"/>
-      <c r="B73" s="117"/>
+      <c r="A73" s="113"/>
+      <c r="B73" s="111"/>
       <c r="C73" s="36" t="s">
         <v>197</v>
       </c>
@@ -3838,8 +3838,8 @@
       <c r="K73" s="28"/>
     </row>
     <row r="74" spans="1:11" s="29" customFormat="1" ht="198" x14ac:dyDescent="0.3">
-      <c r="A74" s="131"/>
-      <c r="B74" s="118"/>
+      <c r="A74" s="113"/>
+      <c r="B74" s="112"/>
       <c r="C74" s="36" t="s">
         <v>200</v>
       </c>
@@ -3847,7 +3847,7 @@
         <v>201</v>
       </c>
       <c r="E74" s="37" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F74" s="36" t="s">
         <v>112</v>
@@ -3861,9 +3861,9 @@
       <c r="K74" s="28"/>
     </row>
     <row r="75" spans="1:11" s="29" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A75" s="131"/>
-      <c r="B75" s="116" t="s">
-        <v>280</v>
+      <c r="A75" s="113"/>
+      <c r="B75" s="110" t="s">
+        <v>279</v>
       </c>
       <c r="C75" s="36" t="s">
         <v>202</v>
@@ -3886,8 +3886,8 @@
       <c r="K75" s="28"/>
     </row>
     <row r="76" spans="1:11" s="29" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A76" s="131"/>
-      <c r="B76" s="117"/>
+      <c r="A76" s="113"/>
+      <c r="B76" s="111"/>
       <c r="C76" s="36" t="s">
         <v>205</v>
       </c>
@@ -3909,8 +3909,8 @@
       <c r="K76" s="28"/>
     </row>
     <row r="77" spans="1:11" s="29" customFormat="1" ht="198" x14ac:dyDescent="0.3">
-      <c r="A77" s="131"/>
-      <c r="B77" s="118"/>
+      <c r="A77" s="113"/>
+      <c r="B77" s="112"/>
       <c r="C77" s="36" t="s">
         <v>208</v>
       </c>
@@ -3918,7 +3918,7 @@
         <v>209</v>
       </c>
       <c r="E77" s="37" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F77" s="36" t="s">
         <v>112</v>
@@ -3933,8 +3933,8 @@
     </row>
     <row r="78" spans="1:11" s="29" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A78"/>
-      <c r="B78" s="116" t="s">
-        <v>281</v>
+      <c r="B78" s="110" t="s">
+        <v>280</v>
       </c>
       <c r="C78" s="106" t="s">
         <v>210</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="79" spans="1:11" s="33" customFormat="1" ht="92.4" x14ac:dyDescent="0.3">
       <c r="A79"/>
-      <c r="B79" s="118"/>
+      <c r="B79" s="112"/>
       <c r="C79" s="106" t="s">
         <v>213</v>
       </c>
@@ -3966,7 +3966,7 @@
         <v>214</v>
       </c>
       <c r="E79" s="106" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F79" s="106" t="s">
         <v>114</v>
@@ -3980,11 +3980,11 @@
       <c r="K79" s="32"/>
     </row>
     <row r="80" spans="1:11" s="33" customFormat="1" ht="141.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="131" t="s">
+      <c r="A80" s="113" t="s">
+        <v>293</v>
+      </c>
+      <c r="B80" s="110" t="s">
         <v>294</v>
-      </c>
-      <c r="B80" s="116" t="s">
-        <v>295</v>
       </c>
       <c r="C80" s="36" t="s">
         <v>215</v>
@@ -3993,7 +3993,7 @@
         <v>216</v>
       </c>
       <c r="E80" s="106" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F80" s="36" t="s">
         <v>112</v>
@@ -4007,19 +4007,19 @@
       <c r="K80" s="32"/>
     </row>
     <row r="81" spans="1:11" s="33" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="131"/>
-      <c r="B81" s="117"/>
+      <c r="A81" s="113"/>
+      <c r="B81" s="111"/>
       <c r="C81" s="36" t="s">
+        <v>297</v>
+      </c>
+      <c r="D81" s="37" t="s">
         <v>298</v>
       </c>
-      <c r="D81" s="37" t="s">
-        <v>299</v>
-      </c>
       <c r="E81" s="37" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F81" s="36" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G81" s="36" t="s">
         <v>270</v>
@@ -4030,19 +4030,19 @@
       <c r="K81" s="32"/>
     </row>
     <row r="82" spans="1:11" s="33" customFormat="1" ht="212.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="131"/>
-      <c r="B82" s="118"/>
+      <c r="A82" s="113"/>
+      <c r="B82" s="112"/>
       <c r="C82" s="36" t="s">
+        <v>299</v>
+      </c>
+      <c r="D82" s="37" t="s">
         <v>300</v>
       </c>
-      <c r="D82" s="37" t="s">
+      <c r="E82" s="37" t="s">
+        <v>337</v>
+      </c>
+      <c r="F82" s="36" t="s">
         <v>301</v>
-      </c>
-      <c r="E82" s="37" t="s">
-        <v>338</v>
-      </c>
-      <c r="F82" s="36" t="s">
-        <v>302</v>
       </c>
       <c r="G82" s="36"/>
       <c r="H82" s="31"/>
@@ -4051,11 +4051,11 @@
       <c r="K82" s="32"/>
     </row>
     <row r="83" spans="1:11" s="33" customFormat="1" ht="117" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="131" t="s">
-        <v>294</v>
-      </c>
-      <c r="B83" s="116" t="s">
-        <v>296</v>
+      <c r="A83" s="113" t="s">
+        <v>293</v>
+      </c>
+      <c r="B83" s="110" t="s">
+        <v>295</v>
       </c>
       <c r="C83" s="36" t="s">
         <v>217</v>
@@ -4064,7 +4064,7 @@
         <v>218</v>
       </c>
       <c r="E83" s="106" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F83" s="36" t="s">
         <v>112</v>
@@ -4078,19 +4078,19 @@
       <c r="K83" s="32"/>
     </row>
     <row r="84" spans="1:11" s="33" customFormat="1" ht="83.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="131"/>
-      <c r="B84" s="117"/>
+      <c r="A84" s="113"/>
+      <c r="B84" s="111"/>
       <c r="C84" s="36" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D84" s="37" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E84" s="37" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F84" s="36" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G84" s="36" t="s">
         <v>270</v>
@@ -4101,19 +4101,19 @@
       <c r="K84" s="32"/>
     </row>
     <row r="85" spans="1:11" s="33" customFormat="1" ht="199.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="131"/>
-      <c r="B85" s="118"/>
+      <c r="A85" s="113"/>
+      <c r="B85" s="112"/>
       <c r="C85" s="36" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D85" s="37" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E85" s="37" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F85" s="36" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G85" s="36"/>
       <c r="H85" s="31"/>
@@ -4122,8 +4122,8 @@
       <c r="K85" s="32"/>
     </row>
     <row r="86" spans="1:11" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="B86" s="116" t="s">
-        <v>282</v>
+      <c r="B86" s="110" t="s">
+        <v>281</v>
       </c>
       <c r="C86" s="36" t="s">
         <v>227</v>
@@ -4132,17 +4132,17 @@
         <v>228</v>
       </c>
       <c r="E86" s="106" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F86" s="36" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G86" s="36" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="B87" s="117"/>
+      <c r="B87" s="111"/>
       <c r="C87" s="36" t="s">
         <v>229</v>
       </c>
@@ -4150,7 +4150,7 @@
         <v>230</v>
       </c>
       <c r="E87" s="106" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F87" s="36" t="s">
         <v>112</v>
@@ -4160,7 +4160,7 @@
       </c>
     </row>
     <row r="88" spans="1:11" ht="198" x14ac:dyDescent="0.3">
-      <c r="B88" s="117"/>
+      <c r="B88" s="111"/>
       <c r="C88" s="36" t="s">
         <v>231</v>
       </c>
@@ -4168,17 +4168,17 @@
         <v>232</v>
       </c>
       <c r="E88" s="106" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F88" s="36" t="s">
-        <v>276</v>
+        <v>367</v>
       </c>
       <c r="G88" s="36" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="66" x14ac:dyDescent="0.3">
-      <c r="B89" s="118"/>
+      <c r="B89" s="112"/>
       <c r="C89" s="36" t="s">
         <v>233</v>
       </c>
@@ -4229,6 +4229,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="E17:E26"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="B83:B85"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="B55:B58"/>
+    <mergeCell ref="B59:B62"/>
+    <mergeCell ref="B63:B66"/>
+    <mergeCell ref="B67:B71"/>
+    <mergeCell ref="B3:B16"/>
+    <mergeCell ref="B17:B26"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="B30:B41"/>
+    <mergeCell ref="B51:B54"/>
     <mergeCell ref="B86:B89"/>
     <mergeCell ref="A17:A26"/>
     <mergeCell ref="B45:B46"/>
@@ -4245,20 +4259,6 @@
     <mergeCell ref="A80:A82"/>
     <mergeCell ref="B80:B82"/>
     <mergeCell ref="A83:A85"/>
-    <mergeCell ref="B3:B16"/>
-    <mergeCell ref="B17:B26"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="B30:B41"/>
-    <mergeCell ref="B51:B54"/>
-    <mergeCell ref="E17:E26"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="B83:B85"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="B55:B58"/>
-    <mergeCell ref="B59:B62"/>
-    <mergeCell ref="B63:B66"/>
-    <mergeCell ref="B67:B71"/>
   </mergeCells>
   <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4296,7 +4296,7 @@
         <v>15</v>
       </c>
       <c r="E1" s="91" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F1" s="91" t="s">
         <v>20</v>
@@ -4368,10 +4368,10 @@
         <v>80</v>
       </c>
       <c r="AC1" s="93" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AD1" s="93" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AE1" s="93" t="s">
         <v>86</v>
@@ -4506,7 +4506,7 @@
         <v>236</v>
       </c>
       <c r="BW1" s="45" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="BX1" s="45" t="s">
         <v>170</v>
@@ -4530,7 +4530,7 @@
         <v>238</v>
       </c>
       <c r="CE1" s="45" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="CF1" s="45" t="s">
         <v>188</v>
@@ -4539,13 +4539,13 @@
         <v>191</v>
       </c>
       <c r="CH1" s="109" t="s">
+        <v>342</v>
+      </c>
+      <c r="CI1" s="109" t="s">
         <v>343</v>
       </c>
-      <c r="CI1" s="109" t="s">
-        <v>344</v>
-      </c>
       <c r="CJ1" s="109" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="CK1" s="45" t="s">
         <v>193</v>
@@ -4575,91 +4575,91 @@
         <v>215</v>
       </c>
       <c r="CT1" s="45" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="CU1" s="45" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="CV1" s="45" t="s">
         <v>217</v>
       </c>
       <c r="CW1" s="45" t="s">
+        <v>302</v>
+      </c>
+      <c r="CX1" s="45" t="s">
         <v>303</v>
-      </c>
-      <c r="CX1" s="45" t="s">
-        <v>304</v>
       </c>
       <c r="CY1" s="45" t="s">
         <v>219</v>
       </c>
       <c r="CZ1" s="45" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="DA1" s="45" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="DB1" s="45" t="s">
         <v>220</v>
       </c>
       <c r="DC1" s="45" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="DD1" s="45" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="DE1" s="45" t="s">
         <v>221</v>
       </c>
       <c r="DF1" s="45" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="DG1" s="45" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="DH1" s="45" t="s">
         <v>222</v>
       </c>
       <c r="DI1" s="45" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="DJ1" s="45" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="DK1" s="45" t="s">
         <v>223</v>
       </c>
       <c r="DL1" s="45" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="DM1" s="45" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="DN1" s="45" t="s">
         <v>224</v>
       </c>
       <c r="DO1" s="45" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="DP1" s="45" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="DQ1" s="45" t="s">
         <v>225</v>
       </c>
       <c r="DR1" s="45" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="DS1" s="45" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="DT1" s="45" t="s">
         <v>226</v>
       </c>
       <c r="DU1" s="45" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="DV1" s="45" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="DW1" s="45" t="s">
         <v>227</v>
@@ -20408,15 +20408,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="42fbd5e6-b175-407a-a25c-5fc6410bf24f" xsi:nil="true"/>
@@ -20425,6 +20416,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20447,14 +20447,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{286F673D-E70D-4002-B8F5-CAC95B029A7E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E9485EC-5D88-4A1C-961D-0F4FE84359B8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -20463,4 +20455,12 @@
     <ds:schemaRef ds:uri="a20b3d4d-24e9-4db7-bf1d-acbd8c10320e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{286F673D-E70D-4002-B8F5-CAC95B029A7E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>